--- a/AAII_Financials/Quarterly/FANDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FANDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>FANDY</t>
   </si>
@@ -656,74 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +775,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +828,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +881,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +906,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +955,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +1008,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1061,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1114,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1136,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1185,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1238,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1263,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1312,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1365,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1418,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1471,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1524,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1577,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1630,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1683,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1736,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1789,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1842,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1895,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1948,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +2001,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +2054,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2107,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2190,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2211,487 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5554700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5336700</v>
+      </c>
+      <c r="F41" s="3">
         <v>8783900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8419700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7099600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6861200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7107800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7777900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6462500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6244700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6419300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6223500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5665500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>6023800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6434500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6071800</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13795800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13254400</v>
+      </c>
+      <c r="F42" s="3">
         <v>13914900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13338000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>9226300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>8916400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8153800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>8922500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>6578700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>6356900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>8158300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>7909500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>8248200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>8769800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>8817100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>8320100</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>830400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>797800</v>
+      </c>
+      <c r="F43" s="3">
         <v>35000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>33600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>584800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>565200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>50700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>55500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>543000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>524700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>65700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>63700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>393400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>418200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>91700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>2500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2400</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>3000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>3800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33077100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>31779000</v>
+      </c>
+      <c r="F45" s="3">
         <v>375600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>360000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2108400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2037600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>863900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>945300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2095400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2024700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>736800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>714300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2500800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2658900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1038000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>979500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56318600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>54108400</v>
+      </c>
+      <c r="F46" s="3">
         <v>25705400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>24639600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21624100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20897800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18384300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20117400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18092600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17482700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17761300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17219500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19134000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20343900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18575100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17528000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27412800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>26337000</v>
+      </c>
+      <c r="F47" s="3">
         <v>30101100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>28853000</v>
       </c>
-      <c r="F47" s="3">
-        <v>28581700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>27621800</v>
-      </c>
       <c r="H47" s="3">
+        <v>28707400</v>
+      </c>
+      <c r="I47" s="3">
+        <v>27743300</v>
+      </c>
+      <c r="J47" s="3">
         <v>26807300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>29334500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>24367700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>23546300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>24385500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>23641700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>22969700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>24422100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>24348600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>22976100</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1461000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1403600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1439100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1379400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1331900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1287200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1275700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1396000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1277800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1234700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1204700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1168000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1123100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1194200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1194300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1126900</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>131100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>126000</v>
+      </c>
+      <c r="F49" s="3">
         <v>585000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>560700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>582800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>563200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>535900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>586400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>531400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>513500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>552000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>535100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>545600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>580100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>550800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>519700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2737,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2790,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>645200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>619800</v>
+      </c>
+      <c r="F52" s="3">
         <v>3645300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3494200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>523700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>506200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1887600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2065600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>349300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>337600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>876700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>850000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>260500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>276900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>788800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>744400</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2896,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>167270200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>160705700</v>
+      </c>
+      <c r="F54" s="3">
         <v>161970000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>155254300</v>
       </c>
-      <c r="F54" s="3">
-        <v>145665500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>140773200</v>
-      </c>
       <c r="H54" s="3">
+        <v>145791200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>140894600</v>
+      </c>
+      <c r="J54" s="3">
         <v>134682300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>147379300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>129652300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>125282000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>127682700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>123788300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>122005700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>129720600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>126049300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>118944000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2974,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2995,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101438200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>97457300</v>
+      </c>
+      <c r="F57" s="3">
         <v>136246200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>130597100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>109591600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>105910900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>114364500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>125146100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>98235200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>94923900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>108152900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>104854100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>89788000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>95465600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>105481800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>99535900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4132700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3970500</v>
+      </c>
+      <c r="F58" s="3">
         <v>4766000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4568400</v>
       </c>
-      <c r="F58" s="3">
-        <v>5479800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5295800</v>
-      </c>
       <c r="H58" s="3">
+        <v>5485500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5301200</v>
+      </c>
+      <c r="J58" s="3">
         <v>2699200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2953600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3742200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3616100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2639600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2559100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5110900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5434100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3491800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3295000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29001400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>27863200</v>
+      </c>
+      <c r="F59" s="3">
         <v>623600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>597700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1113900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1076500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>953800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1043700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>711100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>687200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>729500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>707300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>747100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>794300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1004000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>947400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>135690400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>130365300</v>
+      </c>
+      <c r="F60" s="3">
         <v>142304600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>136404200</v>
       </c>
-      <c r="F60" s="3">
-        <v>117292300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>113353000</v>
-      </c>
       <c r="H60" s="3">
+        <v>117298000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>113358400</v>
+      </c>
+      <c r="J60" s="3">
         <v>118628700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>129812200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>103755200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>100257800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>112169300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>108748100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>96720400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>102836400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>110675200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>104436500</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14719500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>14141800</v>
+      </c>
+      <c r="F61" s="3">
         <v>2007500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1924300</v>
       </c>
-      <c r="F61" s="3">
-        <v>13491100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>13038000</v>
-      </c>
       <c r="H61" s="3">
+        <v>13485500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>13032600</v>
+      </c>
+      <c r="J61" s="3">
         <v>1444500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1580700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13043500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12603900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>965300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>935900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>13797300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>14669700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1199000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1131400</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1525400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1465600</v>
+      </c>
+      <c r="F62" s="3">
         <v>2678000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2567000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1029300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>994700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2386100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2611000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>799300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>772300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3023000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2930800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>680000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>723000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3533000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3333800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3362,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3415,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3468,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>152266900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>146291200</v>
+      </c>
+      <c r="F66" s="3">
         <v>147054900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>140957600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>132094600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>127658100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>122504800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>134053800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>117859400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>113886600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>116211800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>112667300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>111470600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>118519300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>115440100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>108932800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3546,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3595,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3648,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3701,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3754,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12392200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>11905900</v>
+      </c>
+      <c r="F72" s="3">
         <v>12401800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>11887600</v>
       </c>
-      <c r="F72" s="3">
-        <v>10954900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>10587000</v>
-      </c>
       <c r="H72" s="3">
+        <v>11030100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>10659600</v>
+      </c>
+      <c r="J72" s="3">
         <v>9928700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>10864700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>9704500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9377400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>9342700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>9057700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8628400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9174000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9044400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>8534600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3860,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3913,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3966,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14642700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14068100</v>
+      </c>
+      <c r="F76" s="3">
         <v>14580300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>13975800</v>
       </c>
-      <c r="F76" s="3">
-        <v>13265500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>12819900</v>
-      </c>
       <c r="H76" s="3">
+        <v>13391200</v>
+      </c>
+      <c r="I76" s="3">
+        <v>12941400</v>
+      </c>
+      <c r="J76" s="3">
         <v>11907200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13029800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11526600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11138100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11221100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10878800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>10307500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10959200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>10360900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9776800</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +4072,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +4183,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4208,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>55700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>60900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>62400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>60300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>56000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>54300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>55500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>59000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>57500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>54300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>61800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>69100</v>
       </c>
       <c r="P83" s="3">
         <v>61800</v>
       </c>
       <c r="Q83" s="3">
+        <v>69100</v>
+      </c>
+      <c r="R83" s="3">
+        <v>61800</v>
+      </c>
+      <c r="S83" s="3">
         <v>65800</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4310,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4363,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4416,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4469,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4522,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
         <v>827300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>793000</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3919600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-3788000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>398700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>436200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1350700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1305200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-411300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-398700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3618500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3847300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>319800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4600,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>-240300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-230300</v>
       </c>
-      <c r="F91" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-122800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-134400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-94800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-91600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-79200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-76800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-65800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-69900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-66200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-62500</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4702,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4755,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>-212800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-204000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-61100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-59100</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>-83000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-90900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-124900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-120700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-39100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-37900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-60500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-64300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-55900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,8 +4833,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4380,11 +4846,11 @@
       <c r="E96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="3">
-        <v>731900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>707300</v>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
@@ -4392,32 +4858,38 @@
       <c r="I96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>648500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>626600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>772700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>821600</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4935,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4988,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +5041,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
         <v>97300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>93300</v>
       </c>
-      <c r="F100" s="3">
-        <v>3565900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>3446100</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>105900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>115900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2278700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2201900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>72700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>70400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>4752200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>5052800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-176000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-166000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>39800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>43500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-196000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-189400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>67300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>65300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-75200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-79900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-10900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-10300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>17300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>19300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>127300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>605100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>580100</v>
       </c>
-      <c r="F102" s="3">
-        <v>-211800</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-204600</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>461300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>504800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>607100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>586700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-310400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-300900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>998100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1061200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>73600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>69500</v>
       </c>
     </row>
